--- a/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 직원 회의 중에 흥분해서 낙상 예방 훈련을 시연하는 걸 하게 됐어요. 의자를 이리저리 옮기고 팔을 휘두르고 있었는데, 사람들이 앉으라고 했는데도 멈출 수가… 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 최근에 유난히 에너지가 넘치거나 과잉행동을 하는 느낌이 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 그런 날에는 일찍부터 시작해요—옷장을 정리하고, 돌봄 체크리스트를 다시 쓰고, 교회 건강 박람회 계획을 세우고요. 아침 먹기도 전에 사람들한테 전화를 걸기 시작해요, 지금 당장 다 해야 할 것처럼 느껴지거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다른 사람들은 보거나 듣지 못하는 걸 보거나 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 가끔은요, 네. 복도나 집 세탁실 근처에 혼자 있을 때, 제 이름을 부르는 소리나 입소자가 도움을 요청하는 소리가 들려요. 아주 또렷하게 들리는데, 가서 확인해 보면 아무도 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 살면서 몇 주 이상 심하게 우울하거나 흥미를 잃었던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네… 아내가 그러는데 제가 그냥 거실에 앉아서 소리를 낮춰 놓은 TV를 보고만 있을 때가 있대요. 교회 친구들한테 전화도 안 하고, 예전처럼 간단한 집안일도 제대로 못 해요, 해야 한다는 걸 알면서도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 기분과 에너지가 완전히 정상이었던 시기에도 그런 목소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 좀 더 차분했던 시기가 있었는데, 그때는 잠도 꽤 정상적으로 자고 여러 프로젝트를 벌이며 바쁘게 돌아다니지도 않았는데, 그런데도 몇 주 동안 제 이름을 부르는 소리가 계속 들렸어요. 그리고 직장 사람들이 저에 대한 기록을 남기고 있다는 확신도 계속 들었고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (양극형) (D006)
 인구통계: 성별 남성 / 나이 41 / 직업상태 personal care aide / 최종학력 고등학교 중퇴
@@ -575,200 +684,52 @@
 증상 지속 기간: 1 year and 5 months
 추가 요건: psychotic_symptoms and manic_episode occur concurrently, manic_episode is present for the majority of the total duration of the active and residual portions of the illness, delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode
 주호소 증상 코드: S022
-배경 서술: 매튜의 어려움은 노인 센터의 새 상사가 그의 문서 작성 방식을 비판하고 그가 늘 맡아 왔던 여러 안전 교육을 다른 사람에게 재배정하면서 시작되었는데, 그는 이를 믿음직한 돌봄 제공자로서의 정체성에 핵심적인 역할에 대한 공개적인 신뢰 상실로 받아들였다. 이후 1년 5개월에 걸쳐, 평소의 정돈된 그의 모습은 유난히 의욕적인 활동, 짧은 수면, 건강 워크숍과 교회 프로젝트에 대한 과도한 계획, 그리고 평온한 시기에도 이어지는 고정된 의심성 믿음이 번갈아 나타나는 시기로 바뀌었고, 가족과 동료들도 이상한 행동, 사회적 위축, 뒤따르지 못하는 일 처리를 알아챘다. 그가 직원 회의를 안전 절차에 대한 부적절하고 흥분된 시연으로 방해한 뒤 휴직 처분을 받고, 이어서 예전에는 꼼꼼히 처리하던 환자 돌봄 절차를 놓치기 시작하면서 이 변화는 임상적으로 유의미한 수준이 되었다. 고용주가 돌봄 업무 복귀 전 정신과 소견을 요구하면서, 그의 아내와 목사가 그가 지역 정신건강 클리닉을 통한 평가를 받아들이도록 도왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 직원 회의 중에 흥분해서 낙상 예방 훈련을 시연하는 걸 하게 됐어요. 의자를 이리저리 옮기고 팔을 휘두르고 있었는데, 사람들이 앉으라고 했는데도 멈출 수가… 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 최근에 유난히 에너지가 넘치거나 과잉행동을 하는 느낌이 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 그런 날에는 일찍부터 시작해요—옷장을 정리하고, 돌봄 체크리스트를 다시 쓰고, 교회 건강 박람회 계획을 세우고요. 아침 먹기도 전에 사람들한테 전화를 걸기 시작해요, 지금 당장 다 해야 할 것처럼 느껴지거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다른 사람들은 보거나 듣지 못하는 걸 보거나 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 가끔은요, 네. 복도나 집 세탁실 근처에 혼자 있을 때, 제 이름을 부르는 소리나 입소자가 도움을 요청하는 소리가 들려요. 아주 또렷하게 들리는데, 가서 확인해 보면 아무도 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 살면서 몇 주 이상 심하게 우울하거나 흥미를 잃었던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네… 아내가 그러는데 제가 그냥 거실에 앉아서 소리를 낮춰 놓은 TV를 보고만 있을 때가 있대요. 교회 친구들한테 전화도 안 하고, 예전처럼 간단한 집안일도 제대로 못 해요, 해야 한다는 걸 알면서도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 기분과 에너지가 완전히 정상이었던 시기에도 그런 목소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 좀 더 차분했던 시기가 있었는데, 그때는 잠도 꽤 정상적으로 자고 여러 프로젝트를 벌이며 바쁘게 돌아다니지도 않았는데, 그런데도 몇 주 동안 제 이름을 부르는 소리가 계속 들렸어요. 그리고 직장 사람들이 저에 대한 기록을 남기고 있다는 확신도 계속 들었고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 매튜의 어려움은 노인 센터의 새 상사가 그의 문서 작성 방식을 비판하고 그가 늘 맡아 왔던 여러 안전 교육을 다른 사람에게 재배정하면서 시작되었는데, 그는 이를 믿음직한 돌봄 제공자로서의 정체성에 핵심적인 역할에 대한 공개적인 신뢰 상실로 받아들였다. 이후 1년 5개월에 걸쳐, 평소의 정돈된 그의 모습은 유난히 의욕적인 활동, 짧은 수면, 건강 워크숍과 교회 프로젝트에 대한 과도한 계획, 그리고 평온한 시기에도 이어지는 고정된 의심성 믿음이 번갈아 나타나는 시기로 바뀌었고, 가족과 동료들도 이상한 행동, 사회적 위축, 뒤따르지 못하는 일 처리를 알아챘다. 그가 직원 회의를 안전 절차에 대한 부적절하고 흥분된 시연으로 방해한 뒤 휴직 처분을 받고, 이어서 예전에는 꼼꼼히 처리하던 환자 돌봄 절차를 놓치기 시작하면서 이 변화는 임상적으로 유의미한 수준이 되었다. 고용주가 돌봄 업무 복귀 전 정신과 소견을 요구하면서, 그의 아내와 목사가 그가 지역 정신건강 클리닉을 통한 평가를 받아들이도록 도왔다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 조현정동장애 (양극형) (D006, ICD: F25.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.3333</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
-  누락: 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
-  확인된 근거: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 조현정동장애 (양극형) (D006, ICD: F25.0)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: 0.3333
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
+확인된 근거:
+  - 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -725,11 +730,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S005_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2559</v>
+        <v>0.3166</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.2726</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.4762</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
